--- a/accountant-skill/data/output/Jan2026/trial_balance_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/trial_balance_Jan2026.xlsx
@@ -114,7 +114,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -131,11 +131,42 @@
     <border>
       <bottom style="double"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -170,6 +201,33 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,14 +597,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -577,6 +635,10 @@
           <t>TRIAL BALANCE SUMMARY</t>
         </is>
       </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -620,7 +682,7 @@
       <c r="D7" s="8" t="n">
         <v>-1120000</v>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -641,7 +703,7 @@
       <c r="D8" s="8" t="n">
         <v>-1120000</v>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -649,19 +711,23 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>CONTENTS</t>
         </is>
       </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -699,34 +765,38 @@
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>VALIDATION CHECKS</t>
         </is>
       </c>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Total Debit</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Total Credit</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -747,7 +817,7 @@
       <c r="D18" s="8" t="n">
         <v>-1120000</v>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -768,7 +838,7 @@
       <c r="D19" s="8" t="n">
         <v>-1120000</v>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -787,7 +857,7 @@
         <v>87750</v>
       </c>
       <c r="D20" s="7" t="n"/>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -795,11 +865,15 @@
     </row>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>WARNINGS</t>
         </is>
       </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -850,13 +924,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -914,7 +988,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>10000</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -938,7 +1012,7 @@
       <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>10100</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -962,7 +1036,7 @@
       <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="7" t="n">
         <v>11000</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -986,7 +1060,7 @@
       <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>12000</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1010,7 +1084,7 @@
       <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="7" t="n">
         <v>12200</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -1034,7 +1108,7 @@
       <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>12400</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -1058,7 +1132,7 @@
       <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="7" t="n">
         <v>13000</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -1082,7 +1156,7 @@
       <c r="F12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>15100</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -1106,7 +1180,7 @@
       <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="7" t="n">
         <v>15110</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1130,7 +1204,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>15200</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1154,7 +1228,7 @@
       <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="7" t="n">
         <v>15210</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1178,7 +1252,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>15300</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1202,7 +1276,7 @@
       <c r="F17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="7" t="n">
         <v>15310</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1226,7 +1300,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>20000</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1250,7 +1324,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="7" t="n">
         <v>21000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1274,7 +1348,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>22200</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1298,7 +1372,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="7" t="n">
         <v>25000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1322,7 +1396,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>30200</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1346,7 +1420,7 @@
       <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="7" t="n">
         <v>31000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1370,7 +1444,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="7" t="n">
         <v>32000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1394,7 +1468,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="7" t="n">
         <v>40000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1418,7 +1492,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="7" t="n">
         <v>50000</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1442,7 +1516,7 @@
       <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="7" t="n">
         <v>50100</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1466,7 +1540,7 @@
       <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="7" t="n">
         <v>50310</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1490,7 +1564,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="7" t="n">
         <v>60000</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1514,7 +1588,7 @@
       <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="7" t="n">
         <v>61000</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1538,7 +1612,7 @@
       <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="7" t="n">
         <v>62000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1562,7 +1636,7 @@
       <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="7" t="n">
         <v>63000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1586,7 +1660,7 @@
       <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="7" t="n">
         <v>64000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1610,7 +1684,7 @@
       <c r="F34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="7" t="n">
         <v>65000</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1634,7 +1708,7 @@
       <c r="F35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="7" t="n">
         <v>66000</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1656,7 +1730,7 @@
       <c r="F36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="7" t="n">
         <v>70000</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1678,34 +1752,36 @@
       <c r="F37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
       <c r="E38" s="12" t="n">
         <v>20463000</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>21583000</v>
       </c>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
     </row>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Dr = Cr Check</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Dr 20,463,000.00 = Cr 21,583,000.00</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1731,15 +1807,15 @@
   <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1771,6 +1847,15 @@
           <t>INDIVIDUAL ADJUSTING ENTRIES</t>
         </is>
       </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2065,21 +2150,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
+      <c r="B12" s="21" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n">
         <v>87750</v>
       </c>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
       <c r="J12" s="12" t="n">
         <v>87750</v>
       </c>
@@ -2087,39 +2172,44 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>PER-ACCOUNT ADJUSTMENT SUMMARY</t>
         </is>
       </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Account Code</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>Total Dr Adj</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>Total Cr Adj</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>Net Effect on Balance</t>
         </is>
@@ -2139,10 +2229,10 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="24" t="n">
         <v>15000</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="24" t="n">
         <v>18000</v>
       </c>
       <c r="F17" s="8" t="n">
@@ -2164,7 +2254,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="24" t="n">
         <v>18750</v>
       </c>
       <c r="F18" s="7" t="n">
@@ -2186,7 +2276,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n">
+      <c r="E19" s="24" t="n">
         <v>22500</v>
       </c>
       <c r="F19" s="7" t="n">
@@ -2208,7 +2298,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="24" t="n">
         <v>13500</v>
       </c>
       <c r="F20" s="7" t="n">
@@ -2229,7 +2319,7 @@
           <t>Expense</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="24" t="n">
         <v>18000</v>
       </c>
       <c r="E21" s="7" t="n"/>
@@ -2251,7 +2341,7 @@
           <t>Expense</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="24" t="n">
         <v>54750</v>
       </c>
       <c r="E22" s="7" t="n"/>
@@ -2274,7 +2364,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="24" t="n">
         <v>15000</v>
       </c>
       <c r="F23" s="7" t="n">
@@ -2304,13 +2394,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2368,7 +2458,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>10000</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2392,7 +2482,7 @@
       <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>10100</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -2416,7 +2506,7 @@
       <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="7" t="n">
         <v>11000</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -2440,7 +2530,7 @@
       <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>12000</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -2464,7 +2554,7 @@
       <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="7" t="n">
         <v>12200</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -2488,7 +2578,7 @@
       <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>12400</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -2512,7 +2602,7 @@
       <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="7" t="n">
         <v>13000</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -2536,7 +2626,7 @@
       <c r="F12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>15100</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -2560,7 +2650,7 @@
       <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="7" t="n">
         <v>15110</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -2584,7 +2674,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>15200</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -2608,7 +2698,7 @@
       <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="7" t="n">
         <v>15210</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -2632,7 +2722,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>15300</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -2656,7 +2746,7 @@
       <c r="F17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="7" t="n">
         <v>15310</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -2680,7 +2770,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>20000</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -2704,7 +2794,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="7" t="n">
         <v>21000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -2728,7 +2818,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>22200</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -2752,7 +2842,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="7" t="n">
         <v>25000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -2776,7 +2866,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>30200</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -2800,7 +2890,7 @@
       <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="7" t="n">
         <v>31000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -2824,7 +2914,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="7" t="n">
         <v>32000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -2848,7 +2938,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="7" t="n">
         <v>40000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -2872,7 +2962,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="7" t="n">
         <v>50000</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -2896,7 +2986,7 @@
       <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="7" t="n">
         <v>50100</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -2920,7 +3010,7 @@
       <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="7" t="n">
         <v>50310</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -2944,7 +3034,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="7" t="n">
         <v>60000</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -2968,7 +3058,7 @@
       <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="7" t="n">
         <v>61000</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -2992,7 +3082,7 @@
       <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="7" t="n">
         <v>62000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -3016,7 +3106,7 @@
       <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="7" t="n">
         <v>63000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -3040,7 +3130,7 @@
       <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="7" t="n">
         <v>64000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -3064,7 +3154,7 @@
       <c r="F34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="7" t="n">
         <v>65000</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -3088,7 +3178,7 @@
       <c r="F35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="7" t="n">
         <v>66000</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -3112,7 +3202,7 @@
       <c r="F36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="7" t="n">
         <v>70000</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -3136,34 +3226,36 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
       <c r="E38" s="12" t="n">
         <v>20532750</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>21652750</v>
       </c>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
     </row>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Dr = Cr Check</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Dr 20,532,750.00 = Cr 21,652,750.00</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3190,9 +3282,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -3270,7 +3362,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>10000</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -3295,7 +3387,7 @@
       <c r="I6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>10100</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -3324,7 +3416,7 @@
       <c r="I7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="7" t="n">
         <v>11000</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -3349,7 +3441,7 @@
       <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>12000</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -3374,7 +3466,7 @@
       <c r="I9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="7" t="n">
         <v>12200</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -3399,7 +3491,7 @@
       <c r="I10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>12400</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -3424,7 +3516,7 @@
       <c r="I11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="7" t="n">
         <v>13000</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -3449,7 +3541,7 @@
       <c r="I12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>15100</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -3474,7 +3566,7 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="7" t="n">
         <v>15110</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -3501,7 +3593,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>15200</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -3526,7 +3618,7 @@
       <c r="I15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="7" t="n">
         <v>15210</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -3553,7 +3645,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>15300</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -3578,7 +3670,7 @@
       <c r="I17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="7" t="n">
         <v>15310</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -3605,7 +3697,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>20000</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -3630,7 +3722,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="7" t="n">
         <v>21000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -3655,7 +3747,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>22200</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -3680,7 +3772,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="7" t="n">
         <v>25000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -3705,7 +3797,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>30200</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -3730,7 +3822,7 @@
       <c r="I23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="7" t="n">
         <v>31000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -3755,7 +3847,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="7" t="n">
         <v>32000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -3780,7 +3872,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="7" t="n">
         <v>40000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -3805,7 +3897,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="7" t="n">
         <v>50000</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -3830,7 +3922,7 @@
       <c r="I27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="7" t="n">
         <v>50100</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -3855,7 +3947,7 @@
       <c r="I28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="7" t="n">
         <v>50310</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -3880,7 +3972,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="7" t="n">
         <v>60000</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -3905,7 +3997,7 @@
       <c r="I30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="7" t="n">
         <v>61000</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -3930,7 +4022,7 @@
       <c r="I31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="7" t="n">
         <v>62000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -3955,7 +4047,7 @@
       <c r="I32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="7" t="n">
         <v>63000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -3980,7 +4072,7 @@
       <c r="I33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="7" t="n">
         <v>64000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -4005,7 +4097,7 @@
       <c r="I34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="7" t="n">
         <v>65000</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -4032,7 +4124,7 @@
       <c r="I35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="7" t="n">
         <v>66000</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -4057,7 +4149,7 @@
       <c r="I36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="7" t="n">
         <v>70000</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -4082,13 +4174,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
       <c r="D38" s="12" t="n">
         <v>20463000</v>
       </c>
@@ -4110,22 +4202,22 @@
     </row>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Unadj. Dr=Cr</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Adjusted Dr=Cr</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4152,13 +4244,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4182,17 +4274,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Unadjusted TB NOT balanced: Dr 20,463,000.00 vs Cr 21,583,000.00 (diff -1,120,000.00)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="7" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="6" t="inlineStr">

--- a/accountant-skill/data/output/Jan2026/trial_balance_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/trial_balance_Jan2026.xlsx
@@ -12,7 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjustments" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjusted TB" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TB Worksheet" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,17 +64,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF0000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00006100"/>
       <sz val="11"/>
@@ -85,8 +73,13 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -105,16 +98,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -131,42 +119,11 @@
     <border>
       <bottom style="double"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <bottom style="medium"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -187,46 +144,16 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -594,17 +521,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -635,10 +562,6 @@
           <t>TRIAL BALANCE SUMMARY</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -674,17 +597,15 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>20463000</v>
+        <v>21493000</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>21583000</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>-1120000</v>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+        <v>21493000</v>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -695,39 +616,33 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>20532750</v>
+        <v>21562750</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>21652750</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>-1120000</v>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+        <v>21562750</v>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>CONTENTS</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -740,7 +655,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -750,7 +665,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -760,43 +675,39 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>VALIDATION CHECKS</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Total Debit</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Total Credit</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -809,17 +720,15 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>20463000</v>
+        <v>21493000</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>21583000</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>-1120000</v>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+        <v>21493000</v>
+      </c>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -830,17 +739,15 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>20532750</v>
+        <v>21562750</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>21652750</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>-1120000</v>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+        <v>21562750</v>
+      </c>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -857,57 +764,20 @@
         <v>87750</v>
       </c>
       <c r="D20" s="7" t="n"/>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>WARNINGS</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="14" t="n"/>
-      <c r="E22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Unadjusted TB NOT balanced: Dr 20,463,000.00 vs Cr 21,583,000.00 (diff -1,120,000.00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Adjusted TB NOT balanced: Dr 20,532,750.00 vs Cr 21,652,750.00 (diff -1,120,000.00)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -920,17 +790,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,7 +858,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>10000</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -1012,7 +882,7 @@
       <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>10100</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -1036,7 +906,7 @@
       <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>11000</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -1055,12 +925,12 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2605000</v>
+        <v>3360000</v>
       </c>
       <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>12000</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1084,12 +954,12 @@
       <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>12200</v>
+      <c r="A10" s="6" t="n">
+        <v>12300</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Inventory - Finished Goods</t>
+          <t>Inventory Adjustments</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1099,218 +969,218 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Advanced Payments</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>260000</v>
-      </c>
-      <c r="F10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>12400</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Work-in-Progress</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>15100</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n">
-        <v>65000</v>
-      </c>
-      <c r="F11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>13000</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Advanced Payments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>15110</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>15200</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>15100</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Buildings &amp; Structures</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="E14" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>15210</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>15300</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="F13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>15110</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="E16" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>15310</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n">
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15400</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
         <v>500000</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>15200</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>15210</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>15300</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Office &amp; Facility Equipment</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>15310</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n">
-        <v>100000</v>
-      </c>
+      <c r="F18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>20000</v>
+      <c r="A19" s="6" t="n">
+        <v>15410</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Accumulated Depreciation - Electrical &amp; Utility Systems</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1320,16 +1190,16 @@
       </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n">
-        <v>1368000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>21000</v>
+      <c r="A20" s="6" t="n">
+        <v>20000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1344,16 +1214,16 @@
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n">
-        <v>500000</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>22200</v>
+      <c r="A21" s="6" t="n">
+        <v>21000</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Wages Payable</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1368,16 +1238,16 @@
       </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n">
-        <v>205000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>25000</v>
+      <c r="A22" s="6" t="n">
+        <v>22200</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1392,35 +1262,35 @@
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n">
+        <v>205000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Bank Loan</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n">
         <v>2000000</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>30200</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Account 30200</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F23" s="7" t="n"/>
-    </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>31000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1440,11 +1310,11 @@
       </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n">
-        <v>7680000</v>
+        <v>7480000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="6" t="n">
         <v>32000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1468,7 +1338,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="6" t="n">
         <v>40000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1492,12 +1362,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>50000</v>
+      <c r="A27" s="6" t="n">
+        <v>50110</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
+          <t>Purchases Packaging</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1511,108 +1381,108 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>50320</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Direct Materials Used</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
         <v>2096000</v>
       </c>
-      <c r="F27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>50100</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Opening Inventory - Packaging </t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="F28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>53000</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Direct Labor Wages</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n">
-        <v>225000</v>
-      </c>
-      <c r="F28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>50310</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Closing Work-in-Progress</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="E29" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>53100</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Machine Maintenance &amp; Repair Expense</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="E30" s="7" t="n">
+        <v>95000</v>
+      </c>
+      <c r="F30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E31" s="7" t="n">
         <v>120000</v>
       </c>
-      <c r="F30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>61000</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Office Salaries</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>2755000</v>
-      </c>
       <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="6" t="n">
         <v>62000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1636,7 +1506,7 @@
       <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="6" t="n">
         <v>63000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1660,7 +1530,7 @@
       <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="6" t="n">
         <v>64000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1684,7 +1554,7 @@
       <c r="F34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="6" t="n">
         <v>65000</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1703,12 +1573,12 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1468500</v>
+        <v>45000</v>
       </c>
       <c r="F35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="6" t="n">
         <v>66000</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1730,60 +1600,82 @@
       <c r="F36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="6" t="n">
+        <v>68000</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>1328500</v>
+      </c>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="12" t="n">
-        <v>20463000</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>21583000</v>
-      </c>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="22" t="n"/>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n">
+        <v>21493000</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>21493000</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Dr = Cr Check</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Dr 20,463,000.00 = Cr 21,583,000.00</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Dr 21,493,000.00 = Cr 21,493,000.00</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1804,18 +1696,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1847,15 +1739,6 @@
           <t>INDIVIDUAL ADJUSTING ENTRIES</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="14" t="n"/>
-      <c r="I5" s="14" t="n"/>
-      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2037,7 +1920,7 @@
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -2050,7 +1933,7 @@
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>13500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="10">
@@ -2066,39 +1949,39 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Bank Recon</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Bank Interest Earned</t>
+          <t>Depreciation — Office Equipment</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Depreciation Expense</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>15000</v>
+        <v>7500</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Accum. Depr. — Electrical &amp; Utility Systems</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>15000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="11">
@@ -2119,133 +2002,152 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
+          <t>Bank Interest Earned</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Cash at Bank</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>10100</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>ADJ-006</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Bank Recon</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
           <t>Software / Subscription</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Telephone &amp; Internet</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>65000</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G12" s="7" t="n">
         <v>18000</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Cash at Bank</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>10100</t>
         </is>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J12" s="7" t="n">
         <v>18000</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n">
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n">
         <v>87750</v>
       </c>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="12" t="n">
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n">
         <v>87750</v>
       </c>
     </row>
-    <row r="13"/>
     <row r="14"/>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>PER-ACCOUNT ADJUSTMENT SUMMARY</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Account Code</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Total Dr Adj</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Total Cr Adj</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Net Effect on Balance</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="n">
-        <v>10100</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Cash at Bank</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>-3000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>15110</v>
+        <v>10100</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -2253,21 +2155,23 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="24" t="n">
-        <v>18750</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>18750</v>
+      <c r="D18" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>-3000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>15210</v>
+        <v>15110</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -2276,20 +2180,20 @@
         </is>
       </c>
       <c r="D19" s="7" t="n"/>
-      <c r="E19" s="24" t="n">
-        <v>22500</v>
+      <c r="E19" s="7" t="n">
+        <v>18750</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>22500</v>
+        <v>18750</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>15310</v>
+        <v>15210</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -2298,86 +2202,130 @@
         </is>
       </c>
       <c r="D20" s="7" t="n"/>
-      <c r="E20" s="24" t="n">
-        <v>13500</v>
+      <c r="E20" s="7" t="n">
+        <v>22500</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>13500</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>65000</v>
+        <v>15310</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="n">
-        <v>18000</v>
-      </c>
-      <c r="E21" s="7" t="n"/>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n">
+        <v>6000</v>
+      </c>
       <c r="F21" s="7" t="n">
-        <v>18000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>66000</v>
+        <v>15410</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Depreciation Expenses - SG&amp;A</t>
+          <t>Accumulated Depreciation - Electrical &amp; Utility Systems</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="n">
-        <v>54750</v>
-      </c>
-      <c r="E22" s="7" t="n"/>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n">
+        <v>7500</v>
+      </c>
       <c r="F22" s="7" t="n">
-        <v>54750</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>66000</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation Expenses - SG&amp;A</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>54750</v>
+      </c>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n">
+        <v>54750</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="24" t="n">
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F25" s="7" t="n">
         <v>15000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2390,17 +2338,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2458,7 +2406,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>10000</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2482,7 +2430,7 @@
       <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>10100</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -2506,7 +2454,7 @@
       <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>11000</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -2525,12 +2473,12 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2605000</v>
+        <v>3360000</v>
       </c>
       <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>12000</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -2554,12 +2502,12 @@
       <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>12200</v>
+      <c r="A10" s="6" t="n">
+        <v>12300</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Inventory - Finished Goods</t>
+          <t>Inventory Adjustments</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -2569,218 +2517,218 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Advanced Payments</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>260000</v>
-      </c>
-      <c r="F10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>12400</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Work-in-Progress</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>15100</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n">
-        <v>65000</v>
-      </c>
-      <c r="F11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>13000</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Advanced Payments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>15110</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n">
+        <v>518750</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>15200</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>15100</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Buildings &amp; Structures</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="E14" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>15210</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n">
+        <v>472500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>15300</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="F13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>15110</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="E16" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>15310</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n">
-        <v>518750</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>15200</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n">
+        <v>166000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15400</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>15210</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n">
-        <v>472500</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>15300</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Office &amp; Facility Equipment</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n">
+      <c r="E18" s="7" t="n">
         <v>500000</v>
       </c>
-      <c r="F17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>15310</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n">
-        <v>113500</v>
-      </c>
+      <c r="F18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>20000</v>
+      <c r="A19" s="6" t="n">
+        <v>15410</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Accumulated Depreciation - Electrical &amp; Utility Systems</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2790,16 +2738,16 @@
       </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n">
-        <v>1368000</v>
+        <v>107500</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>21000</v>
+      <c r="A20" s="6" t="n">
+        <v>20000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -2814,16 +2762,16 @@
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n">
-        <v>500000</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>22200</v>
+      <c r="A21" s="6" t="n">
+        <v>21000</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Wages Payable</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -2838,16 +2786,16 @@
       </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n">
-        <v>205000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>25000</v>
+      <c r="A22" s="6" t="n">
+        <v>22200</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -2862,35 +2810,35 @@
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n">
+        <v>205000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Bank Loan</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n">
         <v>2000000</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>30200</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Account 30200</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F23" s="7" t="n"/>
-    </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>31000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -2910,11 +2858,11 @@
       </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n">
-        <v>7680000</v>
+        <v>7480000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="6" t="n">
         <v>32000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -2938,7 +2886,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="6" t="n">
         <v>40000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -2962,12 +2910,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>50000</v>
+      <c r="A27" s="6" t="n">
+        <v>50110</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
+          <t>Purchases Packaging</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -2981,108 +2929,108 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>50320</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Direct Materials Used</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
         <v>2096000</v>
       </c>
-      <c r="F27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>50100</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Opening Inventory - Packaging </t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="F28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>53000</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Direct Labor Wages</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n">
-        <v>225000</v>
-      </c>
-      <c r="F28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>50310</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Closing Work-in-Progress</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="E29" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>53100</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Machine Maintenance &amp; Repair Expense</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="E30" s="7" t="n">
+        <v>95000</v>
+      </c>
+      <c r="F30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E31" s="7" t="n">
         <v>120000</v>
       </c>
-      <c r="F30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>61000</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Office Salaries</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>2755000</v>
-      </c>
       <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="6" t="n">
         <v>62000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -3106,7 +3054,7 @@
       <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="6" t="n">
         <v>63000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -3130,7 +3078,7 @@
       <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="6" t="n">
         <v>64000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -3154,7 +3102,7 @@
       <c r="F34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="6" t="n">
         <v>65000</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -3173,12 +3121,12 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1486500</v>
+        <v>63000</v>
       </c>
       <c r="F35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="6" t="n">
         <v>66000</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -3202,62 +3150,84 @@
       <c r="F36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="6" t="n">
+        <v>68000</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>1328500</v>
+      </c>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n">
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="12" t="n">
-        <v>20532750</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>21652750</v>
-      </c>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="22" t="n"/>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n">
+        <v>21562750</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>21562750</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Dr = Cr Check</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Dr 20,532,750.00 = Cr 21,652,750.00</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Dr 21,562,750.00 = Cr 21,562,750.00</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3278,13 +3248,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -3362,7 +3332,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>10000</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -3387,7 +3357,7 @@
       <c r="I6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>10100</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -3416,7 +3386,7 @@
       <c r="I7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>11000</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -3430,18 +3400,18 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2605000</v>
+        <v>3360000</v>
       </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n">
-        <v>2605000</v>
+        <v>3360000</v>
       </c>
       <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>12000</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -3466,12 +3436,12 @@
       <c r="I9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>12200</v>
+      <c r="A10" s="6" t="n">
+        <v>12300</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Inventory - Finished Goods</t>
+          <t>Inventory Adjustments</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3479,24 +3449,24 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>260000</v>
-      </c>
-      <c r="E10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n">
+        <v>15000</v>
+      </c>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n">
-        <v>260000</v>
-      </c>
-      <c r="I10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n">
+        <v>15000</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>12400</v>
+      <c r="A11" s="6" t="n">
+        <v>13000</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Work-in-Progress</t>
+          <t>Advanced Payments</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3505,23 +3475,23 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>65000</v>
+        <v>100000</v>
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n">
-        <v>65000</v>
+        <v>100000</v>
       </c>
       <c r="I11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>13000</v>
+      <c r="A12" s="6" t="n">
+        <v>15100</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Advanced Payments</t>
+          <t>Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -3530,23 +3500,23 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="I12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>15100</v>
+      <c r="A13" s="6" t="n">
+        <v>15110</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Buildings &amp; Structures</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -3554,24 +3524,26 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n">
+        <v>500000</v>
+      </c>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="I13" s="7" t="n"/>
+      <c r="G13" s="7" t="n">
+        <v>18750</v>
+      </c>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n">
+        <v>518750</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>15110</v>
+      <c r="A14" s="6" t="n">
+        <v>15200</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
+          <t>Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -3579,155 +3551,155 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n">
+      <c r="D14" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>15210</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n">
+        <v>22500</v>
+      </c>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n">
+        <v>472500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>15300</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>15310</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n">
+        <v>166000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15400</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
         <v>500000</v>
       </c>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n">
-        <v>18750</v>
-      </c>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n">
-        <v>518750</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>15200</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="I15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>15210</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n">
-        <v>450000</v>
-      </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n">
-        <v>22500</v>
-      </c>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n">
-        <v>472500</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>15300</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Office &amp; Facility Equipment</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n">
         <v>500000</v>
       </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="I17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>15310</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n">
-        <v>13500</v>
-      </c>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n">
-        <v>113500</v>
-      </c>
+      <c r="I18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>20000</v>
+      <c r="A19" s="6" t="n">
+        <v>15410</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Accumulated Depreciation - Electrical &amp; Utility Systems</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>1368000</v>
+        <v>100000</v>
       </c>
       <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
+      <c r="G19" s="7" t="n">
+        <v>7500</v>
+      </c>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n">
-        <v>1368000</v>
+        <v>107500</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>21000</v>
+      <c r="A20" s="6" t="n">
+        <v>20000</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -3737,22 +3709,22 @@
       </c>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>500000</v>
+        <v>1368000</v>
       </c>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n">
-        <v>500000</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>22200</v>
+      <c r="A21" s="6" t="n">
+        <v>21000</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Wages Payable</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -3762,22 +3734,22 @@
       </c>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n">
-        <v>205000</v>
+        <v>500000</v>
       </c>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n">
-        <v>205000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>25000</v>
+      <c r="A22" s="6" t="n">
+        <v>22200</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -3787,42 +3759,42 @@
       </c>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n">
-        <v>2000000</v>
+        <v>205000</v>
       </c>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n">
+        <v>205000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Bank Loan</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n">
         <v>2000000</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>30200</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Account 30200</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="I23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n">
+        <v>2000000</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>31000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -3837,17 +3809,17 @@
       </c>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n">
-        <v>7680000</v>
+        <v>7480000</v>
       </c>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n">
-        <v>7680000</v>
+        <v>7480000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="6" t="n">
         <v>32000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -3872,7 +3844,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="6" t="n">
         <v>40000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -3897,12 +3869,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>50000</v>
+      <c r="A27" s="6" t="n">
+        <v>50110</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
+          <t>Purchases Packaging</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -3911,48 +3883,48 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2096000</v>
+        <v>225000</v>
       </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="I27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>50320</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Direct Materials Used</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
         <v>2096000</v>
-      </c>
-      <c r="I27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>50100</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Opening Inventory - Packaging </t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>225000</v>
       </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n">
-        <v>225000</v>
+        <v>2096000</v>
       </c>
       <c r="I28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>50310</v>
+      <c r="A29" s="6" t="n">
+        <v>53000</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Closing Work-in-Progress</t>
+          <t>Direct Labor Wages</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -3960,24 +3932,24 @@
           <t>Expense</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n">
-        <v>65000</v>
-      </c>
+      <c r="D29" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n">
-        <v>65000</v>
-      </c>
+      <c r="H29" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="I29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>60000</v>
+      <c r="A30" s="6" t="n">
+        <v>53100</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Marketing &amp; Advertising Expense</t>
+          <t>Machine Maintenance &amp; Repair Expense</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -3986,43 +3958,43 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>120000</v>
+        <v>95000</v>
       </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="7" t="n">
+        <v>95000</v>
+      </c>
+      <c r="I30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Advertising Expense</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
         <v>120000</v>
-      </c>
-      <c r="I30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>61000</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Office Salaries</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>2755000</v>
       </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n">
-        <v>2755000</v>
+        <v>120000</v>
       </c>
       <c r="I31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="6" t="n">
         <v>62000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -4047,7 +4019,7 @@
       <c r="I32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="6" t="n">
         <v>63000</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -4072,7 +4044,7 @@
       <c r="I33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="6" t="n">
         <v>64000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -4097,7 +4069,7 @@
       <c r="I34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="6" t="n">
         <v>65000</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -4111,7 +4083,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>1468500</v>
+        <v>45000</v>
       </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n">
@@ -4119,12 +4091,12 @@
       </c>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="7" t="n">
-        <v>1486500</v>
+        <v>63000</v>
       </c>
       <c r="I35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="6" t="n">
         <v>66000</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -4149,77 +4121,102 @@
       <c r="I36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>70000</v>
+      <c r="A37" s="6" t="n">
+        <v>68000</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="n"/>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>1328500</v>
+      </c>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n">
+        <v>1328500</v>
+      </c>
+      <c r="I37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>70000</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="7" t="n">
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="12" t="n">
-        <v>20463000</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>21583000</v>
-      </c>
-      <c r="F38" s="12" t="n">
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n">
+        <v>21493000</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>21493000</v>
+      </c>
+      <c r="F39" s="10" t="n">
         <v>87750</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G39" s="10" t="n">
         <v>87750</v>
       </c>
-      <c r="H38" s="12" t="n">
-        <v>20532750</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>21652750</v>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="H39" s="10" t="n">
+        <v>21562750</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>21562750</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Unadj. Dr=Cr</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Adjusted Dr=Cr</t>
         </is>
       </c>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -4231,72 +4228,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FF0000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Exceptions &amp; Warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Exception / Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Unadjusted TB NOT balanced: Dr 20,463,000.00 vs Cr 21,583,000.00 (diff -1,120,000.00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Adjusted TB NOT balanced: Dr 20,532,750.00 vs Cr 21,652,750.00 (diff -1,120,000.00)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>